--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N3_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N3_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>73.62733372405086</v>
+        <v>11.96444173015827</v>
       </c>
       <c r="D2" t="n">
-        <v>14.67568746155135</v>
+        <v>2.384799212502095</v>
       </c>
       <c r="E2" t="n">
-        <v>14.9254855057541</v>
+        <v>2.425391394685041</v>
       </c>
       <c r="F2" t="n">
-        <v>24.14837396435235</v>
+        <v>3.924110769207257</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>83.08446307331434</v>
+        <v>13.50122524941358</v>
       </c>
       <c r="D3" t="n">
-        <v>24.51208822470664</v>
+        <v>3.98321433651483</v>
       </c>
       <c r="E3" t="n">
-        <v>14.9254855057541</v>
+        <v>2.425391394685041</v>
       </c>
       <c r="F3" t="n">
-        <v>24.14837396435235</v>
+        <v>3.924110769207257</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.48315201570086</v>
+        <v>6.09101220255139</v>
       </c>
       <c r="D4" t="n">
-        <v>55.31631222822759</v>
+        <v>8.988900737086984</v>
       </c>
       <c r="E4" t="n">
-        <v>14.9254855057541</v>
+        <v>2.425391394685041</v>
       </c>
       <c r="F4" t="n">
-        <v>24.14837396435235</v>
+        <v>3.924110769207257</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>62.54842017869292</v>
+        <v>10.1641182790376</v>
       </c>
       <c r="D5" t="n">
-        <v>37.85828839237189</v>
+        <v>6.151971863760433</v>
       </c>
       <c r="E5" t="n">
-        <v>14.9254855057541</v>
+        <v>2.425391394685041</v>
       </c>
       <c r="F5" t="n">
-        <v>24.14837396435235</v>
+        <v>3.924110769207257</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>80.68200028432999</v>
+        <v>13.11082504620362</v>
       </c>
       <c r="D6" t="n">
-        <v>33.01514803843835</v>
+        <v>5.364961556246233</v>
       </c>
       <c r="E6" t="n">
-        <v>14.9254855057541</v>
+        <v>2.425391394685041</v>
       </c>
       <c r="F6" t="n">
-        <v>24.14837396435235</v>
+        <v>3.924110769207257</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>53.02102516242554</v>
+        <v>8.615916588894152</v>
       </c>
       <c r="D7" t="n">
-        <v>77.55203827724326</v>
+        <v>12.60220622005203</v>
       </c>
       <c r="E7" t="n">
-        <v>14.9254855057541</v>
+        <v>2.425391394685041</v>
       </c>
       <c r="F7" t="n">
-        <v>24.14837396435235</v>
+        <v>3.924110769207257</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>62.5790556031621</v>
+        <v>10.16909653551384</v>
       </c>
       <c r="D8" t="n">
-        <v>82.3786987030021</v>
+        <v>13.38653853923784</v>
       </c>
       <c r="E8" t="n">
-        <v>14.9254855057541</v>
+        <v>2.425391394685041</v>
       </c>
       <c r="F8" t="n">
-        <v>24.14837396435235</v>
+        <v>3.924110769207257</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
